--- a/src/data/militancia/militancia-corrigido.xlsx
+++ b/src/data/militancia/militancia-corrigido.xlsx
@@ -1345,7 +1345,7 @@
         <v>Caruaru</v>
       </c>
       <c r="D56" t="str">
-        <v>Idianópolis</v>
+        <v>Indianópolis</v>
       </c>
       <c r="E56" t="str">
         <v>+55 81 9440-4019</v>
@@ -1362,7 +1362,7 @@
         <v>Caruaru</v>
       </c>
       <c r="D57" t="str">
-        <v>Indianapolis</v>
+        <v>Indianópolis</v>
       </c>
       <c r="E57" t="str">
         <v>+55 81 9653-4040</v>

--- a/src/data/militancia/militancia-corrigido.xlsx
+++ b/src/data/militancia/militancia-corrigido.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E130"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2303,9 +2303,315 @@
         <v>+55 81 99457-0435</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Alanna Maria</v>
+      </c>
+      <c r="B113" t="str">
+        <v>DEVG</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Jardim São Paulo</v>
+      </c>
+      <c r="E113" t="str">
+        <v>+55 81 8428-1105</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Aline Roberta</v>
+      </c>
+      <c r="B114" t="str">
+        <v>CAJ</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Paulista</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Aurora</v>
+      </c>
+      <c r="E114" t="str">
+        <v>+55 81 98619-9127</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Edinéa Sousa</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Policial Militar</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Torrões</v>
+      </c>
+      <c r="E115" t="str">
+        <v>+55 81 9950-8337</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Maria Luiza</v>
+      </c>
+      <c r="B116" t="str">
+        <v>CAJ</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Paulista</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Maranguape 2</v>
+      </c>
+      <c r="E116" t="str">
+        <v>+55 81 8266-0946</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Patricia Dayse</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Assistente Social</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Ibura</v>
+      </c>
+      <c r="E117" t="str">
+        <v>+55 81 8515-1850</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Anna Clara</v>
+      </c>
+      <c r="B118" t="str">
+        <v>GERAI</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Paulista</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Arthur Lundreg</v>
+      </c>
+      <c r="E118" t="str">
+        <v>+55 81 9636-2930</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Gledsa Alves</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Assistente de Gerência</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Paulista</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Jaguarana</v>
+      </c>
+      <c r="E119" t="str">
+        <v>+55 81 8862-2609</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>David</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Auxiliar Serviços Gerais</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Paulista</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Maranguape 1</v>
+      </c>
+      <c r="E120" t="str">
+        <v>+55 81 9628-1697</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Ana Nery</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Auxiliar Serviços Gerais</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Jaboatão dos Guararapes</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Curado 3</v>
+      </c>
+      <c r="E121" t="str">
+        <v>+55 81 9695-8563</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Geny Dione</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Vigilante</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Engenho do Meio</v>
+      </c>
+      <c r="E122" t="str">
+        <v>+55 81 8355-8902</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Girleide Maia</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Técnico Admnistrativo</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Varzea</v>
+      </c>
+      <c r="E123" t="str">
+        <v>+55 81 8684-4553</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Itamar Belarmino</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Vigilante</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Varzea</v>
+      </c>
+      <c r="E124" t="str">
+        <v>+55 81 9700-1063</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Lucia Gominho</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Ouvidora da Mulher</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Torrões</v>
+      </c>
+      <c r="E125" t="str">
+        <v>+55 81 8885-0633</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Thamires Rayane da Silva</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Técnico Admnistrativo</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Cabo de Santo Agostinho</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Garapu</v>
+      </c>
+      <c r="E126" t="str">
+        <v>+55 81 8894-4811</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Valmir nestor</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Vigilante</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Pina</v>
+      </c>
+      <c r="E127" t="str">
+        <v>+55 81 8795-3819</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Veronica Perreira</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Auxiliar Serviços Gerais</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Casa Amarela</v>
+      </c>
+      <c r="E128" t="str">
+        <v>+55 81 8415-7185</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Wilma de Assis Neres</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Copeira</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Recife</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Ibura</v>
+      </c>
+      <c r="E129" t="str">
+        <v>+55 81 8549-3417</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Elaine Leticia</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Estagiária</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Cabo de Santo Agostinho</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Pavão</v>
+      </c>
+      <c r="E130" t="str">
+        <v>+55 81 98977-4810</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E130"/>
   </ignoredErrors>
 </worksheet>
 </file>